--- a/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD882AAD-F6C6-4062-8337-3E96DEAEC147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7E1EE2-E844-4659-BF23-1C59C5F7AFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1776" yWindow="1776" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>Name</t>
   </si>
@@ -84,6 +84,10 @@
   </si>
   <si>
     <t>[{"IntentId":1,"Value":4}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntentEntry[]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -650,8 +654,8 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7E1EE2-E844-4659-BF23-1C59C5F7AFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB533C64-01EF-48E2-AEE7-A33719E07643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="1776" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2124" yWindow="2124" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -67,10 +67,6 @@
     <t>践踏</t>
   </si>
   <si>
-    <t>[{"IntentId":0,"Value":1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"IntentId":1,"Value":7}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -88,6 +84,10 @@
   </si>
   <si>
     <t>IntentEntry[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":0,"Value":-1}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -655,7 +655,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -677,7 +677,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -688,7 +688,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -699,7 +699,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -707,10 +707,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB533C64-01EF-48E2-AEE7-A33719E07643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E25BD01-90E1-4C17-BE28-0D5D51F3BCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2124" yWindow="2124" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -31,63 +31,129 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Intents</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>意图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":1,"Value":7}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":1,"Value":13}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲撞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":1,"Value":4}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntentEntry[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":0,"Value":-1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>名称</t>
-  </si>
-  <si>
-    <t>Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Intents</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>缩小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>意图</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>大啃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>践踏</t>
-  </si>
-  <si>
-    <t>[{"IntentId":1,"Value":7}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"IntentId":1,"Value":13}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冲撞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"IntentId":1,"Value":4}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntentEntry[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"IntentId":0,"Value":-1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黏糊射击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>戳刺扑击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞扑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>啄击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>墨迹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>墨水长枪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肢解</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>准备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":2,"Value":4}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":1,"Value":11}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":1,"Value":17}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":1,"Value":9}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":1,"Value":12}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":1,"Value":26},{"IntentId":2,"Value":4}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":3,"Value":3}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -628,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -637,81 +703,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/ActionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E25BD01-90E1-4C17-BE28-0D5D51F3BCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE7233F-2B9E-45A4-BD4C-E12B882485FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3516" yWindow="3516" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionConfig" sheetId="1" r:id="rId1"/>
@@ -69,10 +69,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"IntentId":0,"Value":-1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -154,6 +150,10 @@
   </si>
   <si>
     <t>[{"IntentId":3,"Value":3}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"IntentId":0,"Value":4}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -707,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -715,10 +715,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -743,7 +743,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -762,7 +762,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -784,10 +784,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -806,10 +806,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -817,10 +817,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -828,7 +828,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -839,10 +839,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -850,10 +850,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -861,10 +861,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
